--- a/projeto-captura-de-leads/Esboço tabela dados no Banco de Dados.xlsx
+++ b/projeto-captura-de-leads/Esboço tabela dados no Banco de Dados.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\ESTUDOS\DevMedia\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D970328-A6DF-4C94-A46E-8F9638F98DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5E502DC2-1435-4EBA-A1B1-3C6D00A09EA2}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -71,8 +65,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,7 +217,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -275,7 +269,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -489,22 +483,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{102D4F5E-A742-4FF6-AD55-54F9DD35D825}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" customWidth="1"/>
+    <col min="3" max="3" width="16.75" customWidth="1"/>
+    <col min="4" max="4" width="22.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -518,7 +513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -532,7 +527,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -546,7 +541,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" s="4">
         <v>3</v>
       </c>
